--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Brazil/eps-brazil-3.4.8/InputData/elec/MPCbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/elec/MPCbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55EA03D-587F-EC45-BAD7-9C2AE5377378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3287EE27-3CDF-6046-A158-DF9E360CD9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="MPCbS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>Source:</t>
   </si>
@@ -116,12 +113,6 @@
   </si>
   <si>
     <t>this limit doesn't come into play for these three electricity sources.)</t>
-  </si>
-  <si>
-    <t>Installed Capacity (MW)</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>https://www.epe.gov.br/sites-pt/publicacoes-dados-abertos/publicacoes/PublicacoesArquivos/publicacao-227/topico-416/NT04%20PR_RecursosEnergeticos%202050.pdf</t>
@@ -204,7 +195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -212,10 +203,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -237,47 +224,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="sum"/>
-      <sheetName val="BD siga"/>
-      <sheetName val="hidro"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="12">
-          <cell r="F12">
-            <v>16745977</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="F13">
-            <v>29515521</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="F15">
-            <v>109883925</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="F17">
-            <v>12294847</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,12 +529,12 @@
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -598,7 +544,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -652,7 +598,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -663,24 +609,22 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
-        <f>[1]sum!$F$15/1000</f>
-        <v>109883.925</v>
-      </c>
-      <c r="C3" s="5">
-        <v>176000</v>
+      <c r="B3" s="6">
+        <v>1760000</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1760000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="5">
-        <f>[1]sum!$F$13/1000</f>
-        <v>29515.521000000001</v>
-      </c>
-      <c r="C4" s="5">
-        <v>179000</v>
+      <c r="B4" s="6">
+        <v>1790000</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1790000</v>
       </c>
       <c r="D4" s="4"/>
     </row>
@@ -688,56 +632,54 @@
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5">
-        <v>514000</v>
+      <c r="B5" s="6">
+        <v>5140000</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5140000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <f>[1]sum!$F$17/1000</f>
-        <v>12294.847</v>
-      </c>
-      <c r="C6" s="5">
-        <v>340000</v>
+      <c r="B6" s="6">
+        <v>3400000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3400000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5">
-        <v>140000</v>
+      <c r="B7" s="6">
+        <v>1400000</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1400000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5">
-        <f>[1]sum!$F$12/1000</f>
-        <v>16745.976999999999</v>
-      </c>
-      <c r="C8" s="5">
-        <v>20000</v>
+      <c r="B8" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2000000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="6">
         <v>0</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>0</v>
       </c>
     </row>
@@ -745,27 +687,27 @@
       <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <v>0</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>30</v>
+      <c r="A12" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +739,7 @@
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <f>9*10^12</f>
         <v>9000000000000</v>
       </c>
@@ -806,7 +748,7 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <f>9*10^12</f>
         <v>9000000000000</v>
       </c>
@@ -815,7 +757,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <f>9*10^12</f>
         <v>9000000000000</v>
       </c>
@@ -824,52 +766,52 @@
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <f>Data!C3</f>
-        <v>176000</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="7">
         <f>Data!C4</f>
-        <v>179000</v>
+        <v>1790000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <f>Data!C6</f>
-        <v>340000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <f>Data!C7</f>
-        <v>140000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <f>Data!C8</f>
-        <v>20000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="7">
         <f>Data!C9</f>
         <v>0</v>
       </c>
@@ -878,7 +820,7 @@
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <f>9*10^12</f>
         <v>9000000000000</v>
       </c>
@@ -887,7 +829,7 @@
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <f>9*10^12</f>
         <v>9000000000000</v>
       </c>
@@ -896,7 +838,7 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <f>B2</f>
         <v>9000000000000</v>
       </c>
@@ -905,16 +847,16 @@
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <f>Data!C5</f>
-        <v>514000</v>
+        <v>5140000</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <f>B11</f>
         <v>9000000000000</v>
       </c>
@@ -923,7 +865,7 @@
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <f>B11</f>
         <v>9000000000000</v>
       </c>
@@ -932,7 +874,7 @@
       <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <f>Data!C10</f>
         <v>0</v>
       </c>
